--- a/output/pdf_financials_xlsx/LUXX.xlsx
+++ b/output/pdf_financials_xlsx/LUXX.xlsx
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">

--- a/output/pdf_financials_xlsx/LUXX.xlsx
+++ b/output/pdf_financials_xlsx/LUXX.xlsx
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-2.793741</v>
       </c>
     </row>
     <row r="117">
@@ -2694,7 +2694,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>-0.124656</v>
       </c>
@@ -2830,7 +2834,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
